--- a/source/09_GenerativeAI_RPA/1-1_xlwings_test.xlsx
+++ b/source/09_GenerativeAI_RPA/1-1_xlwings_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huhjuang\Dropbox\강의\03_멀티캠퍼스_GSC\28_20241030_ChatGPT_RPA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\source\09_GenerativeAI_RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239200D8-3346-4F0C-87B5-EF069EE1D361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8F78FA-D1C8-4D35-9EC3-0E008F9626E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="0" windowWidth="12840" windowHeight="13700" xr2:uid="{2E1D0062-3B68-410B-A7E4-394B76FC3C19}"/>
+    <workbookView xWindow="4968" yWindow="2652" windowWidth="17280" windowHeight="8964" xr2:uid="{2E1D0062-3B68-410B-A7E4-394B76FC3C19}"/>
   </bookViews>
   <sheets>
     <sheet name="계산서" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -432,9 +430,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327CD44A-9D89-44CB-A086-E17DD33A32C0}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,7 +440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -450,9 +448,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
+      </c>
+      <c r="B3">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
